--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tri.nguyen\Downloads\TRI NGUYEN\Ca nhan\99Tech_QA Lead_Coding changelange\demoblaze-e2e\demoblaze-e2e\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97A8B0D-EC7C-4302-A707-19209DCB28F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5786FC-17E5-4B3D-AE6F-DD55492FB24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1F2EEE7E-83EB-4A86-8019-159212BE9892}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1F2EEE7E-83EB-4A86-8019-159212BE9892}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1384,9 +1384,6 @@
     <t>Alert 'Please fill out Name and Creditcard.'. no order</t>
   </si>
   <si>
-    <t>Redirected to home page. cart is empty</t>
-  </si>
-  <si>
     <t>Month: 13, 00, 'ab'. Year: 1999, 'xx'</t>
   </si>
   <si>
@@ -1415,6 +1412,9 @@
   </si>
   <si>
     <t>Guest order is accepted without login</t>
+  </si>
+  <si>
+    <t>Cart is empty after the purchase</t>
   </si>
 </sst>
 </file>
@@ -2516,7 +2516,7 @@
         <v>31</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -2540,7 +2540,7 @@
         <v>34</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -2548,7 +2548,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -2611,7 +2611,7 @@
         <v>34</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M1" s="12" t="s">
         <v>44</v>
@@ -3217,7 +3217,7 @@
         <v>111</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>18</v>
@@ -3955,7 +3955,7 @@
         <v>34</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M1" s="12" t="s">
         <v>44</v>
@@ -4168,7 +4168,7 @@
         <v>199</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>17</v>
@@ -5036,7 +5036,7 @@
         <v>285</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="K26" s="14" t="s">
         <v>17</v>
@@ -5167,7 +5167,7 @@
         <v>189</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I29" s="14" t="s">
         <v>301</v>
@@ -5383,7 +5383,7 @@
         <v>14</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H34" s="14" t="s">
         <v>289</v>
@@ -5401,7 +5401,7 @@
         <v>22</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N34" s="16" t="s">
         <v>375</v>
@@ -5617,7 +5617,7 @@
         <v>373</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
@@ -5660,7 +5660,7 @@
         <v>350</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>351</v>
